--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-169</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 703.716,11</t>
-  </si>
-  <si>
-    <t>R$ 3.931,37
-R$ 4.016,74</t>
-  </si>
-  <si>
-    <t>(3.6%)
-(1.4%)</t>
-  </si>
-  <si>
-    <t>44.0</t>
-  </si>
-  <si>
-    <t>(8.0%)</t>
-  </si>
-  <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>(38.3%)</t>
+170</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 709.352,85</t>
+  </si>
+  <si>
+    <t>R$ 3.919,08
+R$ 4.014,85</t>
+  </si>
+  <si>
+    <t>(3.9%)
+(1.5%)</t>
+  </si>
+  <si>
+    <t>43.9</t>
+  </si>
+  <si>
+    <t>(8.1%)</t>
+  </si>
+  <si>
+    <t>3.5%</t>
+  </si>
+  <si>
+    <t>(38.0%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -950,7 +950,7 @@
     <t>26.3</t>
   </si>
   <si>
-    <t>74.9%</t>
+    <t>75.1%</t>
   </si>
   <si>
     <t>8.3%</t>
@@ -965,16 +965,16 @@
     <t>11.5</t>
   </si>
   <si>
-    <t>18.2</t>
-  </si>
-  <si>
-    <t>73.7%</t>
-  </si>
-  <si>
-    <t>-R$ 21.959,38</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>18.1</t>
+  </si>
+  <si>
+    <t>73.8%</t>
+  </si>
+  <si>
+    <t>-R$ 23.900,36</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -6672,7 +6672,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6708,25 +6708,59 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="O42" s="5">
+        <v>3695.7600000000002</v>
+      </c>
+      <c r="P42" s="5">
+        <v>3695.7600000000002</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.0775451523047892</v>
+      </c>
+      <c r="R42" s="7">
+        <v>48</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.066666666666666652</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.3264464142693248</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.046744810269065087</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.064918988245990003</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0072474944260449807</v>
+      </c>
+      <c r="X42" s="8">
+        <v>23.142424242424244</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.87878787878787878</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.8992914893617021</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>3.1919181818181817</v>
+      </c>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="AD42" s="8">
+        <v>15.579796969696968</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.87878787878787878</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -15303,7 +15337,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15656,7 +15690,7 @@
         <v>0</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -27309,7 +27343,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -27345,25 +27379,55 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>1940.98</v>
+      </c>
+      <c r="P207" s="5">
+        <v>1940.98</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>24</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
+      <c r="T207" s="6">
+        <v>0</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.28883347587301261</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.20689909221115105</v>
+      </c>
+      <c r="W207" s="6">
+        <v>0.10874764294325547</v>
+      </c>
+      <c r="X207" s="8">
+        <v>28.600000000000001</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>6.2715291666666664</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>9.57667</v>
+      </c>
       <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="AD207" s="8">
+        <v>23.101669999999999</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.69999999999999996</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-1940.98</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
@@ -912,21 +912,21 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 709.352,85</t>
-  </si>
-  <si>
-    <t>R$ 3.919,08
-R$ 4.014,85</t>
-  </si>
-  <si>
-    <t>(3.9%)
-(1.5%)</t>
+171</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 712.860,36</t>
+  </si>
+  <si>
+    <t>R$ 3.916,82
+R$ 4.011,88</t>
+  </si>
+  <si>
+    <t>(3.8%)
+(1.4%)</t>
   </si>
   <si>
     <t>43.9</t>
@@ -935,10 +935,10 @@
     <t>(8.1%)</t>
   </si>
   <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>(38.0%)</t>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>(37.9%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -947,34 +947,34 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>26.3</t>
-  </si>
-  <si>
-    <t>75.1%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
+    <t>26.4</t>
+  </si>
+  <si>
+    <t>74.9%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
   </si>
   <si>
     <t>4.7</t>
   </si>
   <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>11.5</t>
-  </si>
-  <si>
-    <t>18.1</t>
-  </si>
-  <si>
-    <t>73.8%</t>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>11.6</t>
+  </si>
+  <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>73.5%</t>
   </si>
   <si>
     <t>-R$ 23.900,36</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -6750,7 +6750,9 @@
       <c r="AB42" s="8">
         <v>3.1919181818181817</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="8">
+        <v>8.6252519999999997</v>
+      </c>
       <c r="AD42" s="8">
         <v>15.579796969696968</v>
       </c>
@@ -14184,7 +14186,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14220,25 +14222,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>3507.5100000000002</v>
+      </c>
+      <c r="P102" s="5">
+        <v>3507.5100000000002</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.30009859593458565</v>
+      </c>
+      <c r="R102" s="7">
+        <v>34</v>
+      </c>
+      <c r="S102" s="6">
+        <v>0.096774193548387011</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.3338693831236404</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.028011267252267276</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.017035589349709623</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0065224332931338759</v>
+      </c>
+      <c r="X102" s="8">
+        <v>45.534668000000003</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.64000000000000001</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>9.8181382352941178</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>15.820291304347824</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>25.566289000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>29.978000000000002</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.16</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -15325,7 +15363,9 @@
       <c r="AB111" s="8">
         <v>1.7642857142857142</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>7.5690460000000002</v>
+      </c>
       <c r="AD111" s="8">
         <v>14.542857142857143</v>
       </c>
@@ -17212,7 +17252,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18389,7 +18429,7 @@
         <v>-123.59999999999999</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20671,7 +20711,7 @@
         <v>-1147.6300000000001</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21883,7 +21923,7 @@
         <v>-179.36000000000001</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -27417,7 +27457,9 @@
       <c r="AB207" s="8">
         <v>9.57667</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>16.158332000000001</v>
+      </c>
       <c r="AD207" s="8">
         <v>23.101669999999999</v>
       </c>
@@ -27962,7 +28004,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-171</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 712.860,36</t>
-  </si>
-  <si>
-    <t>R$ 3.916,82
-R$ 4.011,88</t>
-  </si>
-  <si>
-    <t>(3.8%)
+172</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 715.797,19</t>
+  </si>
+  <si>
+    <t>R$ 3.911,46
+R$ 4.005,63</t>
+  </si>
+  <si>
+    <t>(3.9%)
 (1.4%)</t>
   </si>
   <si>
-    <t>43.9</t>
-  </si>
-  <si>
-    <t>(8.1%)</t>
-  </si>
-  <si>
-    <t>3.7%</t>
-  </si>
-  <si>
-    <t>(37.9%)</t>
+    <t>43.8</t>
+  </si>
+  <si>
+    <t>(8.2%)</t>
+  </si>
+  <si>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>(37.7%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -950,10 +950,10 @@
     <t>26.4</t>
   </si>
   <si>
-    <t>74.9%</t>
-  </si>
-  <si>
-    <t>8.6%</t>
+    <t>74.8%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
   </si>
   <si>
     <t>4.7</t>
@@ -971,10 +971,10 @@
     <t>73.5%</t>
   </si>
   <si>
-    <t>-R$ 23.900,36</t>
-  </si>
-  <si>
-    <t>2.94</t>
+    <t>-R$ 23.946,26</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2213,10 +2213,10 @@
         <v>-0.085714285714285743</v>
       </c>
       <c r="T7" s="6">
-        <v>0.34574369744175948</v>
+        <v>0.33819533721455725</v>
       </c>
       <c r="U7" s="6">
-        <v>0.0070369070721570922</v>
+        <v>-0.00051145315504514798</v>
       </c>
       <c r="V7" s="6">
         <v>0.025761224978068428</v>
@@ -8770,7 +8770,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>12.218629</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -16859,7 +16861,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -25941,7 +25943,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25977,25 +25979,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>2936.8299999999999</v>
+      </c>
+      <c r="P195" s="5">
+        <v>2936.8299999999999</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>-0.19281045751633996</v>
+      </c>
+      <c r="R195" s="7">
+        <v>37</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.31481481481481477</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.33826724733811631</v>
+      </c>
+      <c r="U195" s="6">
+        <v>0.041293980244004588</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.035525719908881342</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.0054402195564605378</v>
+      </c>
+      <c r="X195" s="8">
+        <v>26.397529629629631</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.48148148148148145</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>3.9939805555555554</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>7.9153846153846157</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>18.514814814814812</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.7407407407407407</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-45.899999999999999</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-172</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 715.797,19</t>
-  </si>
-  <si>
-    <t>R$ 3.911,46
-R$ 4.005,63</t>
-  </si>
-  <si>
-    <t>(3.9%)
-(1.4%)</t>
-  </si>
-  <si>
-    <t>43.8</t>
+174</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 726.341,60</t>
+  </si>
+  <si>
+    <t>R$ 3.926,17
+R$ 4.020,19</t>
+  </si>
+  <si>
+    <t>(3.7%)
+(1.3%)</t>
+  </si>
+  <si>
+    <t>44.0</t>
   </si>
   <si>
     <t>(8.2%)</t>
   </si>
   <si>
-    <t>3.8%</t>
-  </si>
-  <si>
-    <t>(37.7%)</t>
+    <t>4.1%</t>
+  </si>
+  <si>
+    <t>(37.4%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -950,7 +950,7 @@
     <t>26.4</t>
   </si>
   <si>
-    <t>74.8%</t>
+    <t>74.4%</t>
   </si>
   <si>
     <t>8.5%</t>
@@ -968,10 +968,10 @@
     <t>18.2</t>
   </si>
   <si>
-    <t>73.5%</t>
-  </si>
-  <si>
-    <t>-R$ 23.946,26</t>
+    <t>73.4%</t>
+  </si>
+  <si>
+    <t>-R$ 24.030,76</t>
   </si>
   <si>
     <t>2.95</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>8.7152770833333335</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>16.433644000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>23.143877551020406</v>
       </c>
@@ -8720,7 +8722,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8756,27 +8758,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>4985.4899999999998</v>
+      </c>
+      <c r="P58" s="5">
+        <v>4985.4899999999998</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.099418699527638266</v>
+      </c>
+      <c r="R58" s="7">
+        <v>53</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.01851851851851849</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.60723355176722849</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.24023452057871944</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.015706781078690359</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.002375694264756323</v>
+      </c>
+      <c r="X58" s="8">
+        <v>27.363565116279069</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.39534883720930231</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>3.9731481481481485</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.9608534883720941</v>
+      </c>
       <c r="AC58" s="8">
         <v>12.218629</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>19.236046511627908</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.62790697674418605</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -10950,7 +10986,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10984,25 +11020,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>5558.9200000000001</v>
+      </c>
+      <c r="P76" s="5">
+        <v>5558.9200000000001</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0.095772571189775002</v>
+      </c>
+      <c r="R76" s="7">
+        <v>61</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.14084507042253525</v>
+      </c>
+      <c r="T76" s="6">
+        <v>-0.10423665028458766</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.51442424067984427</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.022560227526210126</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.012232501996790743</v>
+      </c>
+      <c r="X76" s="8">
+        <v>28.372</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.4166672131147537</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>12.358695652173912</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>15.740176</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>23.300668000000002</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-84.5</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -23967,7 +24039,9 @@
       <c r="AB179" s="8">
         <v>1.62395625</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.2612120000000004</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.282293749999999</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
@@ -912,69 +912,69 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 726.341,60</t>
-  </si>
-  <si>
-    <t>R$ 3.926,17
-R$ 4.020,19</t>
-  </si>
-  <si>
-    <t>(3.7%)
-(1.3%)</t>
+176</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 734.776,93</t>
+  </si>
+  <si>
+    <t>R$ 3.929,29
+R$ 4.022,44</t>
+  </si>
+  <si>
+    <t>(4.0%)
+(1.7%)</t>
   </si>
   <si>
     <t>44.0</t>
   </si>
   <si>
-    <t>(8.2%)</t>
-  </si>
-  <si>
-    <t>4.1%</t>
-  </si>
-  <si>
-    <t>(37.4%)</t>
-  </si>
-  <si>
-    <t>4.3%</t>
+    <t>(8.5%)</t>
+  </si>
+  <si>
+    <t>2.2%</t>
+  </si>
+  <si>
+    <t>(39.1%)</t>
+  </si>
+  <si>
+    <t>4.2%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>26.4</t>
-  </si>
-  <si>
-    <t>74.4%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
+    <t>26.5</t>
+  </si>
+  <si>
+    <t>74.3%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
   </si>
   <si>
     <t>4.7</t>
   </si>
   <si>
-    <t>6.9</t>
+    <t>7.0</t>
   </si>
   <si>
     <t>11.6</t>
   </si>
   <si>
-    <t>18.2</t>
-  </si>
-  <si>
-    <t>73.4%</t>
-  </si>
-  <si>
-    <t>-R$ 24.030,76</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>18.3</t>
+  </si>
+  <si>
+    <t>73.1%</t>
+  </si>
+  <si>
+    <t>-R$ 24.085,66</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -4388,7 +4388,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4424,25 +4424,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>4476.5200000000004</v>
+      </c>
+      <c r="P24" s="5">
+        <v>4476.5200000000004</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.028782335312827589</v>
+      </c>
+      <c r="R24" s="7">
+        <v>50</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.038461538461538436</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.32823264500102756</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.024576903487530492</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0017761564786932704</v>
+      </c>
+      <c r="X24" s="8">
+        <v>35.219908333333336</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>4.831973469387755</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>13.464352777777778</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>25.160647222222224</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.3611111111111111</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-54.899999999999999</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5710,10 +5744,10 @@
         <v>-0.36448598130841126</v>
       </c>
       <c r="T34" s="6">
-        <v>0.39668995609335267</v>
+        <v>-1.6641513550333598</v>
       </c>
       <c r="U34" s="6">
-        <v>0.069946100694505811</v>
+        <v>-1.9908952104322066</v>
       </c>
       <c r="V34" s="6">
         <v>0.072687109310362014</v>
@@ -12604,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12643,7 +12677,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12677,25 +12711,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>3958.8099999999999</v>
+      </c>
+      <c r="P89" s="5">
+        <v>3958.8099999999999</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.42546172802238469</v>
+      </c>
+      <c r="R89" s="7">
+        <v>37</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.46376811594202894</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.10731330879734062</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.435242661304786</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.036313311323352221</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.011101189498864558</v>
+      </c>
+      <c r="X89" s="8">
+        <v>34.309375000000003</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>4.1708333333333334</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>9.3354187500000005</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>22.87291875</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16679,7 +16747,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18634,7 +18702,7 @@
         <v>0</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20912,7 +20980,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-16).xlsx
@@ -912,36 +912,36 @@
   </si>
   <si>
     <t>214
-176</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>R$ 734.776,93</t>
-  </si>
-  <si>
-    <t>R$ 3.929,29
-R$ 4.022,44</t>
-  </si>
-  <si>
-    <t>(4.0%)
-(1.7%)</t>
-  </si>
-  <si>
-    <t>44.0</t>
-  </si>
-  <si>
-    <t>(8.5%)</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>(39.1%)</t>
-  </si>
-  <si>
-    <t>4.2%</t>
+180</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 751.039,68</t>
+  </si>
+  <si>
+    <t>R$ 3.932,14
+R$ 4.023,40</t>
+  </si>
+  <si>
+    <t>(3.7%)
+(1.3%)</t>
+  </si>
+  <si>
+    <t>43.9</t>
+  </si>
+  <si>
+    <t>(8.3%)</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>(38.3%)</t>
+  </si>
+  <si>
+    <t>4.3%</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -950,7 +950,7 @@
     <t>26.5</t>
   </si>
   <si>
-    <t>74.3%</t>
+    <t>74.7%</t>
   </si>
   <si>
     <t>8.6%</t>
@@ -959,7 +959,7 @@
     <t>4.7</t>
   </si>
   <si>
-    <t>7.0</t>
+    <t>6.9</t>
   </si>
   <si>
     <t>11.6</t>
@@ -968,7 +968,7 @@
     <t>18.3</t>
   </si>
   <si>
-    <t>73.1%</t>
+    <t>73.3%</t>
   </si>
   <si>
     <t>-R$ 24.085,66</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>10034.540000000001</v>
+      </c>
+      <c r="P6" s="5">
+        <v>10034.540000000001</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.4837233923005495</v>
+      </c>
+      <c r="R6" s="7">
+        <v>102</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.29139963565843574</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.024485297781462825</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.03456015921008835</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0066764694744353001</v>
+      </c>
+      <c r="X6" s="8">
+        <v>22.480591139240506</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.92405063291139244</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>6.5217323529411759</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.4710974683544302</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>9.2326999999999995</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>16.191560759493669</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.93670886075949367</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -5958,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5994,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>2587.9099999999999</v>
+      </c>
+      <c r="P36" s="5">
+        <v>2587.9099999999999</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.10242990524548767</v>
+      </c>
+      <c r="R36" s="7">
+        <v>28</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.15151515151515149</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.37142412216808163</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.086765845798346938</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.20792763272293086</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.13514303047633033</v>
+      </c>
+      <c r="X36" s="8">
+        <v>34.629627777777777</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>8.7919740740740746</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>8.5614562500000009</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>17.559605999999999</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>23.12222222222222</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.61111111111111116</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7879,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7915,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>709.64999999999998</v>
+      </c>
+      <c r="P51" s="5">
+        <v>709.64999999999998</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.26886938245657421</v>
+      </c>
+      <c r="R51" s="7">
+        <v>6</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.40000000000000002</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.29369407454378921</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.023916719509617417</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.15646797717184527</v>
+      </c>
+      <c r="X51" s="8">
+        <v>26.505566666666667</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.0805499999999997</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>11.594433333333333</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>15.449999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>22.405566666666669</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -21374,7 +21482,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21410,25 +21518,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2930.6500000000001</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2930.6500000000001</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.13901146359090666</v>
+      </c>
+      <c r="R158" s="7">
+        <v>29</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.1470588235294118</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.32706515619401838</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.011077235425588181</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.028036613038063225</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.013602613754627813</v>
+      </c>
+      <c r="X158" s="8">
+        <v>31.723809523809525</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>8.4931034482758623</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>3.5785714285714287</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>12.665872</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>19.614285714285714</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.47619047619047616</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
